--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q3" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R3" s="48">
@@ -1445,7 +1445,11 @@
       <c r="V3" s="15" t="n"/>
       <c r="W3" s="15" t="n"/>
       <c r="X3" s="20" t="n"/>
-      <c r="Y3" s="15" t="n"/>
+      <c r="Y3" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-07 → kids-shorts/tiny-sparks/numbers/day-002-learn-numbers-1-10-with-animals/output/day-002-sfx-music.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -1527,7 +1527,7 @@
       </c>
       <c r="Q4" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R4" s="48">
@@ -1543,7 +1543,11 @@
       <c r="V4" s="15" t="n"/>
       <c r="W4" s="15" t="n"/>
       <c r="X4" s="20" t="n"/>
-      <c r="Y4" s="15" t="n"/>
+      <c r="Y4" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-08 → kids-shorts/tiny-sparks/words/day-003-20-animals-in-english-and-french/output/day-003-sfx-music.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -1625,7 +1625,7 @@
       </c>
       <c r="Q5" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R5" s="48">
@@ -1641,7 +1641,11 @@
       <c r="V5" s="15" t="n"/>
       <c r="W5" s="15" t="n"/>
       <c r="X5" s="20" t="n"/>
-      <c r="Y5" s="15" t="n"/>
+      <c r="Y5" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-08 → kids-shorts/tiny-sparks/animals/day-004-rory-the-lion-who-was-afraid-of-the-dark/output/day-004-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Q6" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R6" s="48">
@@ -1739,7 +1739,11 @@
       <c r="V6" s="15" t="n"/>
       <c r="W6" s="15" t="n"/>
       <c r="X6" s="20" t="n"/>
-      <c r="Y6" s="15" t="n"/>
+      <c r="Y6" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/science/day-005-why-is-the-sky-blue/output/day-005-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -1821,7 +1821,7 @@
       </c>
       <c r="Q7" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R7" s="48">
@@ -1837,7 +1837,11 @@
       <c r="V7" s="15" t="n"/>
       <c r="W7" s="15" t="n"/>
       <c r="X7" s="20" t="n"/>
-      <c r="Y7" s="15" t="n"/>
+      <c r="Y7" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/puzzles/day-006-find-the-missing-number/output/day-006-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -1919,7 +1919,7 @@
       </c>
       <c r="Q8" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R8" s="48">
@@ -1935,7 +1935,11 @@
       <c r="V8" s="15" t="n"/>
       <c r="W8" s="15" t="n"/>
       <c r="X8" s="20" t="n"/>
-      <c r="Y8" s="15" t="n"/>
+      <c r="Y8" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/songs/day-007-count-from-1-to-10-song/output/day-007-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Q9" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R9" s="48">
@@ -2033,7 +2033,11 @@
       <c r="V9" s="15" t="n"/>
       <c r="W9" s="15" t="n"/>
       <c r="X9" s="20" t="n"/>
-      <c r="Y9" s="15" t="n"/>
+      <c r="Y9" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/morals/day-008-the-boy-who-always-told-the-truth/output/day-008-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2115,7 +2115,7 @@
       </c>
       <c r="Q10" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R10" s="48">
@@ -2131,7 +2131,11 @@
       <c r="V10" s="15" t="n"/>
       <c r="W10" s="15" t="n"/>
       <c r="X10" s="20" t="n"/>
-      <c r="Y10" s="15" t="n"/>
+      <c r="Y10" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/numbers/day-009-counting-1-20-with-balloons/output/day-009-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2213,7 +2213,7 @@
       </c>
       <c r="Q11" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R11" s="48">
@@ -2229,7 +2229,11 @@
       <c r="V11" s="15" t="n"/>
       <c r="W11" s="15" t="n"/>
       <c r="X11" s="20" t="n"/>
-      <c r="Y11" s="15" t="n"/>
+      <c r="Y11" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/words/day-010-20-colors-in-english-and-french/output/day-010-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Q12" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R12" s="48">
@@ -2327,7 +2327,11 @@
       <c r="V12" s="15" t="n"/>
       <c r="W12" s="15" t="n"/>
       <c r="X12" s="20" t="n"/>
-      <c r="Y12" s="15" t="n"/>
+      <c r="Y12" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/animals/day-011-benny-the-rabbit-and-the-lost-carrot/output/day-011-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2409,7 +2409,7 @@
       </c>
       <c r="Q13" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R13" s="48">
@@ -2425,7 +2425,11 @@
       <c r="V13" s="15" t="n"/>
       <c r="W13" s="15" t="n"/>
       <c r="X13" s="20" t="n"/>
-      <c r="Y13" s="15" t="n"/>
+      <c r="Y13" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/science/day-012-why-does-the-sun-shine/output/day-012-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2507,7 +2507,7 @@
       </c>
       <c r="Q14" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R14" s="48">
@@ -2523,7 +2523,11 @@
       <c r="V14" s="15" t="n"/>
       <c r="W14" s="15" t="n"/>
       <c r="X14" s="20" t="n"/>
-      <c r="Y14" s="15" t="n"/>
+      <c r="Y14" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/puzzles/day-013-find-the-missing-shape/output/day-013-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2605,7 +2605,7 @@
       </c>
       <c r="Q15" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R15" s="48">
@@ -2621,7 +2621,11 @@
       <c r="V15" s="15" t="n"/>
       <c r="W15" s="15" t="n"/>
       <c r="X15" s="20" t="n"/>
-      <c r="Y15" s="15" t="n"/>
+      <c r="Y15" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/songs/day-014-count-from-1-to-20-song/output/day-014-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2703,7 +2703,7 @@
       </c>
       <c r="Q16" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R16" s="48">
@@ -2719,7 +2719,11 @@
       <c r="V16" s="15" t="n"/>
       <c r="W16" s="15" t="n"/>
       <c r="X16" s="20" t="n"/>
-      <c r="Y16" s="15" t="n"/>
+      <c r="Y16" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/stories/day-015-mila-learns-to-say-please-and-thank-you/output/day-015-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2801,7 +2801,7 @@
       </c>
       <c r="Q17" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R17" s="48">
@@ -2817,7 +2817,11 @@
       <c r="V17" s="15" t="n"/>
       <c r="W17" s="15" t="n"/>
       <c r="X17" s="20" t="n"/>
-      <c r="Y17" s="15" t="n"/>
+      <c r="Y17" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/numbers/day-016-counting-apples-1-10/output/day-016-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2899,7 +2899,7 @@
       </c>
       <c r="Q18" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R18" s="48">
@@ -2915,7 +2915,11 @@
       <c r="V18" s="15" t="n"/>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="20" t="n"/>
-      <c r="Y18" s="15" t="n"/>
+      <c r="Y18" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/words/day-017-numbers-1-20-english-french/output/day-017-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -2997,7 +2997,7 @@
       </c>
       <c r="Q19" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R19" s="48">
@@ -3013,7 +3013,11 @@
       <c r="V19" s="15" t="n"/>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="20" t="n"/>
-      <c r="Y19" s="15" t="n"/>
+      <c r="Y19" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/animals/day-018-charlie-the-monkey-s-big-adventure/output/day-018-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3095,7 +3095,7 @@
       </c>
       <c r="Q20" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R20" s="48">
@@ -3111,7 +3111,11 @@
       <c r="V20" s="15" t="n"/>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="20" t="n"/>
-      <c r="Y20" s="15" t="n"/>
+      <c r="Y20" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/science/day-019-why-does-the-moon-glow/output/day-019-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3193,7 +3193,7 @@
       </c>
       <c r="Q21" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R21" s="48">
@@ -3209,7 +3209,11 @@
       <c r="V21" s="15" t="n"/>
       <c r="W21" s="15" t="n"/>
       <c r="X21" s="20" t="n"/>
-      <c r="Y21" s="15" t="n"/>
+      <c r="Y21" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/puzzles/day-020-find-the-missing-color/output/day-020-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="Q22" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R22" s="48">
@@ -3307,7 +3307,11 @@
       <c r="V22" s="15" t="n"/>
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="20" t="n"/>
-      <c r="Y22" s="15" t="n"/>
+      <c r="Y22" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/songs/day-021-alphabet-a-z-song/output/day-021-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Q23" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R23" s="48">
@@ -3405,7 +3405,11 @@
       <c r="V23" s="15" t="n"/>
       <c r="W23" s="15" t="n"/>
       <c r="X23" s="20" t="n"/>
-      <c r="Y23" s="15" t="n"/>
+      <c r="Y23" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/morals/day-022-the-girl-who-learned-to-share/output/day-022-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Q24" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R24" s="48">
@@ -3503,7 +3503,11 @@
       <c r="V24" s="15" t="n"/>
       <c r="W24" s="15" t="n"/>
       <c r="X24" s="20" t="n"/>
-      <c r="Y24" s="15" t="n"/>
+      <c r="Y24" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/numbers/day-023-count-the-cute-puppies/output/day-023-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3585,7 +3585,7 @@
       </c>
       <c r="Q25" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R25" s="48">
@@ -3601,7 +3601,11 @@
       <c r="V25" s="15" t="n"/>
       <c r="W25" s="15" t="n"/>
       <c r="X25" s="20" t="n"/>
-      <c r="Y25" s="15" t="n"/>
+      <c r="Y25" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/words/day-024-family-members-english-french/output/day-024-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Q26" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R26" s="48">
@@ -3699,7 +3699,11 @@
       <c r="V26" s="15" t="n"/>
       <c r="W26" s="15" t="n"/>
       <c r="X26" s="20" t="n"/>
-      <c r="Y26" s="15" t="n"/>
+      <c r="Y26" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/animals/day-025-emma-the-elephant-helps-her-friend/output/day-025-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Q27" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R27" s="48">
@@ -3797,7 +3797,11 @@
       <c r="V27" s="15" t="n"/>
       <c r="W27" s="15" t="n"/>
       <c r="X27" s="20" t="n"/>
-      <c r="Y27" s="15" t="n"/>
+      <c r="Y27" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-09 → kids-shorts/tiny-sparks/science/day-026-why-do-we-have-day-and-night/output/day-026-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3879,7 +3879,7 @@
       </c>
       <c r="Q28" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R28" s="48">
@@ -3895,7 +3895,11 @@
       <c r="V28" s="15" t="n"/>
       <c r="W28" s="15" t="n"/>
       <c r="X28" s="20" t="n"/>
-      <c r="Y28" s="15" t="n"/>
+      <c r="Y28" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/puzzles/day-027-which-animal-doesn-t-belong/output/day-027-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -3977,7 +3977,7 @@
       </c>
       <c r="Q29" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R29" s="48">
@@ -3993,7 +3993,11 @@
       <c r="V29" s="15" t="n"/>
       <c r="W29" s="15" t="n"/>
       <c r="X29" s="20" t="n"/>
-      <c r="Y29" s="15" t="n"/>
+      <c r="Y29" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/songs/day-028-colors-song/output/day-028-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4075,7 +4075,7 @@
       </c>
       <c r="Q30" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R30" s="48">
@@ -4091,7 +4091,11 @@
       <c r="V30" s="15" t="n"/>
       <c r="W30" s="15" t="n"/>
       <c r="X30" s="20" t="n"/>
-      <c r="Y30" s="15" t="n"/>
+      <c r="Y30" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/stories/day-029-bobo-learns-to-clean-his-room/output/day-029-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4173,7 +4173,7 @@
       </c>
       <c r="Q31" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R31" s="48">
@@ -4189,7 +4189,11 @@
       <c r="V31" s="15" t="n"/>
       <c r="W31" s="15" t="n"/>
       <c r="X31" s="20" t="n"/>
-      <c r="Y31" s="15" t="n"/>
+      <c r="Y31" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/numbers/day-030-count-the-colorful-fish/output/day-030-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Q32" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R32" s="48">
@@ -4287,7 +4287,11 @@
       <c r="V32" s="15" t="n"/>
       <c r="W32" s="15" t="n"/>
       <c r="X32" s="20" t="n"/>
-      <c r="Y32" s="15" t="n"/>
+      <c r="Y32" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/words/day-031-fruits-english-french/output/day-031-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Q33" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R33" s="48">
@@ -4385,7 +4385,11 @@
       <c r="V33" s="15" t="n"/>
       <c r="W33" s="15" t="n"/>
       <c r="X33" s="20" t="n"/>
-      <c r="Y33" s="15" t="n"/>
+      <c r="Y33" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/animals/day-032-sammy-the-turtle-learns-patience/output/day-032-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4467,7 +4467,7 @@
       </c>
       <c r="Q34" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R34" s="48">
@@ -4483,7 +4483,11 @@
       <c r="V34" s="15" t="n"/>
       <c r="W34" s="15" t="n"/>
       <c r="X34" s="20" t="n"/>
-      <c r="Y34" s="15" t="n"/>
+      <c r="Y34" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-10 → kids-shorts/tiny-sparks/science/day-033-why-do-seasons-change/output/day-033-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R35" s="48">
@@ -4581,7 +4581,11 @@
       <c r="V35" s="15" t="n"/>
       <c r="W35" s="15" t="n"/>
       <c r="X35" s="20" t="n"/>
-      <c r="Y35" s="15" t="n"/>
+      <c r="Y35" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-21 → kids-shorts/tiny-sparks/puzzles/day-034-which-object-doesn-t-belong/output/day-034-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4663,7 +4663,7 @@
       </c>
       <c r="Q36" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R36" s="48">
@@ -4679,7 +4679,11 @@
       <c r="V36" s="15" t="n"/>
       <c r="W36" s="15" t="n"/>
       <c r="X36" s="20" t="n"/>
-      <c r="Y36" s="15" t="n"/>
+      <c r="Y36" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-21 → kids-shorts/tiny-sparks/songs/day-035-shapes-song/output/day-035-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4761,7 +4761,7 @@
       </c>
       <c r="Q37" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R37" s="48">
@@ -4777,7 +4777,11 @@
       <c r="V37" s="15" t="n"/>
       <c r="W37" s="15" t="n"/>
       <c r="X37" s="20" t="n"/>
-      <c r="Y37" s="15" t="n"/>
+      <c r="Y37" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-21 → kids-shorts/tiny-sparks/morals/day-036-the-greedy-little-monkey/output/day-036-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4859,7 +4859,7 @@
       </c>
       <c r="Q38" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R38" s="48">
@@ -4875,7 +4875,11 @@
       <c r="V38" s="15" t="n"/>
       <c r="W38" s="15" t="n"/>
       <c r="X38" s="20" t="n"/>
-      <c r="Y38" s="15" t="n"/>
+      <c r="Y38" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/numbers/day-037-numbers-1-20-with-dinosaurs/output/day-037-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -4957,7 +4957,7 @@
       </c>
       <c r="Q39" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R39" s="48">
@@ -4973,7 +4973,11 @@
       <c r="V39" s="15" t="n"/>
       <c r="W39" s="15" t="n"/>
       <c r="X39" s="20" t="n"/>
-      <c r="Y39" s="15" t="n"/>
+      <c r="Y39" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/words/day-038-vegetables-english-french/output/day-038-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5055,7 +5055,7 @@
       </c>
       <c r="Q40" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R40" s="48">
@@ -5071,7 +5071,11 @@
       <c r="V40" s="15" t="n"/>
       <c r="W40" s="15" t="n"/>
       <c r="X40" s="20" t="n"/>
-      <c r="Y40" s="15" t="n"/>
+      <c r="Y40" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/animals/day-039-oliver-the-owl-s-first-flight/output/day-039-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5153,7 +5153,7 @@
       </c>
       <c r="Q41" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R41" s="48">
@@ -5169,7 +5169,11 @@
       <c r="V41" s="15" t="n"/>
       <c r="W41" s="15" t="n"/>
       <c r="X41" s="20" t="n"/>
-      <c r="Y41" s="15" t="n"/>
+      <c r="Y41" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/science/day-040-what-are-clouds/output/day-040-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5251,7 +5251,7 @@
       </c>
       <c r="Q42" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R42" s="48">
@@ -5267,7 +5267,11 @@
       <c r="V42" s="15" t="n"/>
       <c r="W42" s="15" t="n"/>
       <c r="X42" s="20" t="n"/>
-      <c r="Y42" s="15" t="n"/>
+      <c r="Y42" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/puzzles/day-041-find-the-different-animal/output/day-041-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Q43" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R43" s="48">
@@ -5365,7 +5365,11 @@
       <c r="V43" s="15" t="n"/>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="20" t="n"/>
-      <c r="Y43" s="15" t="n"/>
+      <c r="Y43" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/songs/day-042-days-of-the-week-song/output/day-042-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5447,7 +5447,7 @@
       </c>
       <c r="Q44" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R44" s="48">
@@ -5463,7 +5463,11 @@
       <c r="V44" s="15" t="n"/>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="20" t="n"/>
-      <c r="Y44" s="15" t="n"/>
+      <c r="Y44" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/stories/day-043-the-day-mila-learned-patience/output/day-043-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Q45" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R45" s="48">
@@ -5561,7 +5561,11 @@
       <c r="V45" s="15" t="n"/>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="20" t="n"/>
-      <c r="Y45" s="15" t="n"/>
+      <c r="Y45" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/numbers/day-044-count-the-farm-animals/output/day-044-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5643,7 +5643,7 @@
       </c>
       <c r="Q46" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R46" s="48">
@@ -5659,7 +5659,11 @@
       <c r="V46" s="15" t="n"/>
       <c r="W46" s="15" t="n"/>
       <c r="X46" s="20" t="n"/>
-      <c r="Y46" s="15" t="n"/>
+      <c r="Y46" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-22 → kids-shorts/tiny-sparks/words/day-045-school-objects-english-french/output/day-045-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -5741,7 +5741,7 @@
       </c>
       <c r="Q47" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R47" s="48">
@@ -5757,7 +5757,11 @@
       <c r="V47" s="15" t="n"/>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="20" t="n"/>
-      <c r="Y47" s="15" t="n"/>
+      <c r="Y47" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/animals/day-046-coco-the-penguin-finds-a-friend/output/day-046-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
@@ -5835,7 +5839,7 @@
       </c>
       <c r="Q48" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R48" s="48">
@@ -5851,7 +5855,11 @@
       <c r="V48" s="15" t="n"/>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="20" t="n"/>
-      <c r="Y48" s="15" t="n"/>
+      <c r="Y48" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/science/day-047-how-does-rain-form/output/day-047-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
@@ -5929,7 +5937,7 @@
       </c>
       <c r="Q49" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R49" s="48">
@@ -5945,7 +5953,11 @@
       <c r="V49" s="15" t="n"/>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="20" t="n"/>
-      <c r="Y49" s="15" t="n"/>
+      <c r="Y49" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/puzzles/day-048-find-the-different-shape/output/day-048-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
@@ -6023,7 +6035,7 @@
       </c>
       <c r="Q50" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R50" s="48">
@@ -6039,7 +6051,11 @@
       <c r="V50" s="15" t="n"/>
       <c r="W50" s="15" t="n"/>
       <c r="X50" s="20" t="n"/>
-      <c r="Y50" s="15" t="n"/>
+      <c r="Y50" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/songs/day-049-months-of-the-year-song/output/day-049-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -6133,7 +6133,7 @@
       </c>
       <c r="Q51" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R51" s="48">
@@ -6149,7 +6149,11 @@
       <c r="V51" s="15" t="n"/>
       <c r="W51" s="15" t="n"/>
       <c r="X51" s="20" t="n"/>
-      <c r="Y51" s="15" t="n"/>
+      <c r="Y51" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/morals/day-050-the-kind-little-rabbit/output/day-050-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="Q52" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R52" s="48">
@@ -6243,7 +6247,11 @@
       <c r="V52" s="15" t="n"/>
       <c r="W52" s="15" t="n"/>
       <c r="X52" s="20" t="n"/>
-      <c r="Y52" s="15" t="n"/>
+      <c r="Y52" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/numbers/day-051-count-the-butterflies/output/day-051-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
@@ -6321,7 +6329,7 @@
       </c>
       <c r="Q53" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R53" s="48">
@@ -6337,7 +6345,11 @@
       <c r="V53" s="15" t="n"/>
       <c r="W53" s="15" t="n"/>
       <c r="X53" s="20" t="n"/>
-      <c r="Y53" s="15" t="n"/>
+      <c r="Y53" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/words/day-052-toys-english-french/output/day-052-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
@@ -6415,7 +6427,7 @@
       </c>
       <c r="Q54" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R54" s="48">
@@ -6431,7 +6443,11 @@
       <c r="V54" s="15" t="n"/>
       <c r="W54" s="15" t="n"/>
       <c r="X54" s="20" t="n"/>
-      <c r="Y54" s="15" t="n"/>
+      <c r="Y54" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/animals/day-053-max-the-dog-saves-the-day/output/day-053-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">

--- a/TINY-SPARKS-CALENDAR.xlsx
+++ b/TINY-SPARKS-CALENDAR.xlsx
@@ -6525,7 +6525,7 @@
       </c>
       <c r="Q55" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R55" s="48">
@@ -6541,7 +6541,11 @@
       <c r="V55" s="15" t="n"/>
       <c r="W55" s="15" t="n"/>
       <c r="X55" s="20" t="n"/>
-      <c r="Y55" s="15" t="n"/>
+      <c r="Y55" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/science/day-054-how-does-snow-form/output/day-054-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
@@ -6619,7 +6623,7 @@
       </c>
       <c r="Q56" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R56" s="48">
@@ -6635,7 +6639,11 @@
       <c r="V56" s="15" t="n"/>
       <c r="W56" s="15" t="n"/>
       <c r="X56" s="20" t="n"/>
-      <c r="Y56" s="15" t="n"/>
+      <c r="Y56" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/puzzles/day-055-find-the-different-number/output/day-055-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
@@ -6713,7 +6721,7 @@
       </c>
       <c r="Q57" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R57" s="48">
@@ -6729,7 +6737,11 @@
       <c r="V57" s="15" t="n"/>
       <c r="W57" s="15" t="n"/>
       <c r="X57" s="20" t="n"/>
-      <c r="Y57" s="15" t="n"/>
+      <c r="Y57" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/songs/day-056-four-seasons-song/output/day-056-final.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
@@ -6807,7 +6819,7 @@
       </c>
       <c r="Q58" s="15" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Rendered</t>
         </is>
       </c>
       <c r="R58" s="48">
@@ -6823,7 +6835,11 @@
       <c r="V58" s="15" t="n"/>
       <c r="W58" s="15" t="n"/>
       <c r="X58" s="20" t="n"/>
-      <c r="Y58" s="15" t="n"/>
+      <c r="Y58" s="15" t="inlineStr">
+        <is>
+          <t>made 2026-10-30 → kids-shorts/tiny-sparks/stories/day-057-leo-learns-why-we-must-listen/output/day-057-sfx-tiny-sparks-bounce.mp4</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
